--- a/outputs/cream/silpo/primary_chain_output.xlsx
+++ b/outputs/cream/silpo/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.166352131060911e-05</v>
+        <v>3.166352131058586e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>1.807358615624225e-13</v>
+        <v>1.807358615622328e-13</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.250471045105603e-20</v>
+        <v>2.250471045106072e-20</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -574,13 +574,13 @@
         <v>0.1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.604635633535988e-13</v>
+        <v>3.604635633536289e-13</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.169300175083072e-11</v>
+        <v>1.169300175082499e-11</v>
       </c>
       <c r="G3" t="n">
         <v>0.09309066682789993</v>
@@ -618,19 +618,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08017296625004949</v>
+        <v>0.08017296625004972</v>
       </c>
       <c r="C4" t="n">
         <v>0.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004821332512077595</v>
+        <v>0.0004821332512077682</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>4.135571752859827e-05</v>
+        <v>4.135571752859924e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
@@ -945,19 +945,19 @@
         <v>3.793680252396324</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3345340871189739</v>
+        <v>0.3345340871189721</v>
       </c>
       <c r="L2" t="n">
         <v>-1.002572700947699</v>
       </c>
       <c r="M2" t="n">
-        <v>2.775901445899018e-16</v>
+        <v>2.775901445894396e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07891071636138866</v>
+        <v>0.07891071636138901</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3144592712848959</v>
+        <v>0.3144592712849068</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
@@ -1024,10 +1024,10 @@
         <v>42</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.02719087049912439</v>
+        <v>-0.02719087049912527</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2713968465337292</v>
+        <v>-0.2713968465337271</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -1098,22 +1098,22 @@
         <v>40</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.070469572016711</v>
+        <v>-0.07046957201671099</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2354291883368252</v>
+        <v>-0.2354291883368262</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.539409399232454</v>
+        <v>-0.5394093992324536</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003540689684816318</v>
+        <v>0.0003540689684874932</v>
       </c>
       <c r="N4" t="n">
-        <v>0.236397565712209</v>
+        <v>0.2363975657122056</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05201532870115675</v>
+        <v>0.05201532870115246</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.889712370853929</v>
+        <v>0.8897123708539287</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2018078467373643</v>
+        <v>0.20180784673736</v>
       </c>
       <c r="G2" t="n">
-        <v>1.393192716168525e-262</v>
+        <v>1.393192716168049e-262</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.004919229359110526</v>
+        <v>0.004919229359111341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5840482434798735</v>
+        <v>0.5840482434845344</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8870969508504547</v>
+        <v>0.8870969508504351</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5530832153948084</v>
+        <v>0.5530832153948044</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6339111636110053</v>
+        <v>0.6339111636110095</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7966413904775785</v>
+        <v>0.7966413904775789</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -57321,10 +57321,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.905619429434132</v>
+        <v>2.905619429434134</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8880608229621922</v>
+        <v>-0.8880608229621898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -57337,10 +57337,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3.166679443444792</v>
+        <v>3.166679443444793</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9678500646420563</v>
+        <v>-0.9678500646420531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>3.190134796965924</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.9750188563770777</v>
+        <v>-0.9750188563770745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57369,10 +57369,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.192242180629738</v>
+        <v>3.192242180629739</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.9756629479094464</v>
+        <v>-0.9756629479094431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>3.192431521877676</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9757208173409214</v>
+        <v>-0.9757208173409182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>3.192448533544221</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9757260167123321</v>
+        <v>-0.9757260167123288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57420,7 +57420,7 @@
         <v>3.192450061984546</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.975726483858153</v>
+        <v>-0.9757264838581496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57433,10 +57433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.192450199309706</v>
+        <v>3.192450199309707</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.9757265258296146</v>
+        <v>-0.9757265258296113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57449,10 +57449,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.192450211647904</v>
+        <v>3.192450211647905</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9757265296006076</v>
+        <v>-0.9757265296006042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57465,10 +57465,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.192450212756449</v>
+        <v>3.19245021275645</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.9757265299394184</v>
+        <v>-0.9757265299394151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57481,10 +57481,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.192450212856048</v>
+        <v>3.192450212856049</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.9757265299698594</v>
+        <v>-0.9757265299698561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>3.192450212864997</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.9757265299725945</v>
+        <v>-0.9757265299725911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>3.192450212865801</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.9757265299728402</v>
+        <v>-0.9757265299728368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>3.192450212865873</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.9757265299728622</v>
+        <v>-0.9757265299728589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.9757265299728642</v>
+        <v>-0.9757265299728609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.9757265299728644</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57612,7 +57612,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -57657,10 +57657,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0464158882449621</v>
+        <v>0.04641588824496175</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1168854602616731</v>
+        <v>0.1168854602616727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -57673,10 +57673,10 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.03956155280035692</v>
+        <v>0.03956155280035661</v>
       </c>
       <c r="C24" t="n">
-        <v>0.09962472943169626</v>
+        <v>0.09962472943169595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -57689,10 +57689,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>0.04057374746394327</v>
+        <v>0.04057374746394295</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1021736591969376</v>
+        <v>0.1021736591969373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -57705,10 +57705,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>0.04042427447049661</v>
+        <v>0.0404242744704963</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1017972531795951</v>
+        <v>0.1017972531795947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -57721,10 +57721,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0404463474734215</v>
+        <v>0.04044634747342119</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1018528378770723</v>
+        <v>0.101852837877072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -57737,10 +57737,10 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04044308790494101</v>
+        <v>0.04044308790494071</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1018446295635723</v>
+        <v>0.101844629563572</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -57753,10 +57753,10 @@
         <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>0.04044356925252726</v>
+        <v>0.04044356925252695</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1018458417031282</v>
+        <v>0.1018458417031279</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -57769,10 +57769,10 @@
         <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>0.04044349817087944</v>
+        <v>0.04044349817087912</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1018456627038364</v>
+        <v>0.1018456627038361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -57785,10 +57785,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="n">
-        <v>0.04044350866766139</v>
+        <v>0.04044350866766108</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1018456891370522</v>
+        <v>0.1018456891370519</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -57801,10 +57801,10 @@
         <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>0.04044350711757871</v>
+        <v>0.0404435071175784</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1018456852336016</v>
+        <v>0.1018456852336013</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -57817,10 +57817,10 @@
         <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0404435073464828</v>
+        <v>0.04044350734648249</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1018456858100327</v>
+        <v>0.1018456858100324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -57833,10 +57833,10 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>0.04044350731268003</v>
+        <v>0.04044350731267972</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1018456857249098</v>
+        <v>0.1018456857249095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -57849,10 +57849,10 @@
         <v>12</v>
       </c>
       <c r="B35" t="n">
-        <v>0.04044350731767176</v>
+        <v>0.04044350731767145</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1018456857374801</v>
+        <v>0.1018456857374798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -57865,10 +57865,10 @@
         <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>0.04044350731693462</v>
+        <v>0.04044350731693431</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1018456857356238</v>
+        <v>0.1018456857356235</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -57881,10 +57881,10 @@
         <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>0.04044350731704348</v>
+        <v>0.04044350731704317</v>
       </c>
       <c r="C37" t="n">
-        <v>0.101845685735898</v>
+        <v>0.1018456857358976</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -57897,10 +57897,10 @@
         <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0404435073170274</v>
+        <v>0.04044350731702709</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1018456857358575</v>
+        <v>0.1018456857358572</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -57913,10 +57913,10 @@
         <v>16</v>
       </c>
       <c r="B39" t="n">
-        <v>0.04044350731702977</v>
+        <v>0.04044350731702946</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1018456857358634</v>
+        <v>0.1018456857358631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -57929,10 +57929,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="n">
-        <v>0.04044350731702942</v>
+        <v>0.04044350731702911</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1018456857358626</v>
+        <v>0.1018456857358623</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -57945,10 +57945,10 @@
         <v>18</v>
       </c>
       <c r="B41" t="n">
-        <v>0.04044350731702948</v>
+        <v>0.04044350731702916</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1018456857358627</v>
+        <v>0.1018456857358624</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -57961,10 +57961,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="n">
-        <v>0.04044350731702947</v>
+        <v>0.04044350731702916</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1018456857358627</v>
+        <v>0.1018456857358624</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -57977,10 +57977,10 @@
         <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>0.04044350731702947</v>
+        <v>0.04044350731702916</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1018456857358627</v>
+        <v>0.1018456857358624</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
